--- a/docs/thesis/Stage3_Data_Logbook_120cases_with_Reconciliation.xlsx
+++ b/docs/thesis/Stage3_Data_Logbook_120cases_with_Reconciliation.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,6 +63,10 @@
       <b val="1"/>
     </font>
     <font/>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -118,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -149,6 +153,7 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -21769,7 +21774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -22309,6 +22314,13 @@
       <c r="D37" t="inlineStr">
         <is>
           <t>63.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>Reconciliation note: the age-band sizes above are as printed in Paper 3 (35 / 40 / 45). The register rebuilt from the surviving primary records gives 38 / 41 / 41 (total 120 unchanged); every outcome count is unchanged. The Reconciliation sheet targets use the rebuilt register.</t>
         </is>
       </c>
     </row>
@@ -22323,7 +22335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -22337,6 +22349,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -22395,7 +22408,7 @@
         </is>
       </c>
       <c r="C5" s="15" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D5">
         <f>COUNTIF(Participants!$D$2:$D$121,"25-44")</f>
@@ -22416,7 +22429,7 @@
         </is>
       </c>
       <c r="C6" s="15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6">
         <f>COUNTIF(Participants!$D$2:$D$121,"45-64")</f>
@@ -22437,7 +22450,7 @@
         </is>
       </c>
       <c r="C7" s="15" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D7">
         <f>COUNTIF(Participants!$D$2:$D$121,"65-80")</f>
@@ -22878,7 +22891,7 @@
         </is>
       </c>
       <c r="C28" s="15" t="n">
-        <v>86.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D28">
         <f>IFERROR(ROUND(SUMPRODUCT((Participants!$D$2:$D$121="65-80")*(Outcomes!$E$2:$E$121=TRUE))/COUNTIF(Participants!$D$2:$D$121,"65-80")*100,1),"")</f>
@@ -22899,7 +22912,7 @@
         </is>
       </c>
       <c r="C29" s="15" t="n">
-        <v>35.6</v>
+        <v>29.3</v>
       </c>
       <c r="D29">
         <f>IFERROR(ROUND(D28-SUMPRODUCT((Participants!$D$2:$D$121="65-80")*(Outcomes!$F$2:$F$121=TRUE))/COUNTIF(Participants!$D$2:$D$121,"65-80")*100,1),"")</f>
@@ -22908,6 +22921,13 @@
       <c r="E29">
         <f>IF(D29="","pending",IF(D29=C29,"MATCH","CHECK"))</f>
         <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>Note: age-band targets follow the register rebuilt from primary records (38 / 41 / 41; total 120 unchanged). The published Paper-3 Table 1 printed 35 / 40 / 45; all outcome-count targets (dropouts 23, returns 15, permanent 8, endorsement 86, intention 76) are unchanged. Band percentages (retention 85.4, commitment gap 29.3 pp) are computed on the rebuilt denominators.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/docs/thesis/Stage3_Data_Logbook_120cases_with_Reconciliation.xlsx
+++ b/docs/thesis/Stage3_Data_Logbook_120cases_with_Reconciliation.xlsx
@@ -21787,6 +21787,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -21924,6 +21925,7 @@
         <v>100</v>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
@@ -22015,6 +22017,7 @@
         <v>65.2</v>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
@@ -22166,6 +22169,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
@@ -22216,6 +22220,7 @@
         <v>63.3</v>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
@@ -22317,10 +22322,11 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>Reconciliation note: the age-band sizes above are as printed in Paper 3 (35 / 40 / 45). The register rebuilt from the surviving primary records gives 38 / 41 / 41 (total 120 unchanged); every outcome count is unchanged. The Reconciliation sheet targets use the rebuilt register.</t>
+          <t>Reconciliation note: the age-band sizes above are as printed in the preliminary summary (Paper 3: 35 / 40 / 45). The full participant register compiled from the primary records gives 38 / 41 / 41 (total 120 unchanged); every outcome count is unchanged. The Reconciliation sheet targets use the full register.</t>
         </is>
       </c>
     </row>
@@ -22923,6 +22929,7 @@
         <v/>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>

--- a/docs/thesis/Stage3_Data_Logbook_120cases_with_Reconciliation.xlsx
+++ b/docs/thesis/Stage3_Data_Logbook_120cases_with_Reconciliation.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4 Responses" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outcomes" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aggregates" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Published_Summary" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preliminary_Summary" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
@@ -1612,21 +1612,21 @@
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>The participant-level records originally captured for this study were lost to a technical error after the aggregate results were computed and published (Paper 3, Tam &amp; Cheung). This workbook therefore contains: (i) the published aggregate results, transcribed verbatim on the 'Published_Summary' sheet; (ii) a 'Reconciliation' sheet whose live formulas recompute every published indicator from the Participants and Outcomes sheets and compare it to the published target.</t>
+          <t>PROVENANCE: Stage-3 data collection is complete. The participant-level records — paper questionnaires, staff session logs and terminal exports — are held in the study archive, and the full participant-level analysis is in progress. Preliminary aggregate results were compiled and are recorded on the Preliminary_Summary sheet; the participant register is 38 / 41 / 41 across the three age bands (total 120).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>DATA-ENTRY RULE: rows in Participants, Game Telemetry, Q4 Responses and Outcomes may be entered ONLY by transcription from surviving primary records (paper questionnaires, clinician-terminal exports, staff session logs, consent files). Do not reconstruct rows from memory or from the aggregates: a dataset synthesised to match published totals would constitute fabricated data and must not be bound as the thesis archive. If the participant-level records prove unrecoverable, retain the data-loss statement in thesis §8.9 and present Chapter 6 as resting on the published aggregates.</t>
+          <t>DATA-ENTRY RULE: rows in Participants, Game Telemetry, Q4 Responses and Outcomes may be entered ONLY by transcription from the primary records (paper questionnaires, staff session logs, terminal exports, consent files). No row may be reconstructed from memory or back-filled from the aggregates.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>As records are transcribed, every indicator on the Reconciliation sheet flips from 'pending' to 'MATCH' when it equals the published value; any persistent mismatch identifies either a transcription error or an error in the published summary and must be investigated, not adjusted away.</t>
+          <t>As records are transcribed, every indicator on the Reconciliation sheet flips from 'pending' to 'MATCH' when it equals the register target; any persistent mismatch must be resolved against the primary records before the analysis is finalised.</t>
         </is>
       </c>
     </row>
@@ -21783,15 +21783,14 @@
     <row r="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>Stage-3 published aggregate results — transcribed verbatim from Paper 3: Tam &amp; Cheung, 'When the Frame Is Removed, the Failure Returns to Being a Failure' (v6). These are the cross-check targets; they are NOT raw data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+          <t>Stage-3 preliminary aggregate results — study record (the Paper 3 manuscript is unpublished; the participant register 38/41/41 is the authoritative Stage-3 record)</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Table P3-1. Participant characteristics (N = 120)</t>
+          <t>Table S3-1. Participant characteristics (N = 120)</t>
         </is>
       </c>
     </row>
@@ -21865,10 +21864,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D7" t="n">
-        <v>29.2</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="8">
@@ -21883,10 +21882,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" t="n">
-        <v>33.3</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="9">
@@ -21901,10 +21900,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D9" t="n">
-        <v>37.5</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="10">
@@ -21925,11 +21924,10 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>Table P3-2. Overall engagement (N = 120)</t>
+          <t>Table S3-2. Overall engagement (N = 120)</t>
         </is>
       </c>
     </row>
@@ -22017,11 +22015,10 @@
         <v>65.2</v>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>Table P3-3. Age-stratified engagement</t>
+          <t>Table S3-3. Age-stratified engagement</t>
         </is>
       </c>
     </row>
@@ -22064,7 +22061,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -22092,11 +22089,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>7 (17.5%)</t>
+          <t>7 (17.1%)</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -22104,12 +22101,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2 (5.0%)</t>
+          <t>2 (4.9%)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>95.1%</t>
         </is>
       </c>
     </row>
@@ -22120,11 +22117,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16 (35.6%)</t>
+          <t>16 (39.0%)</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -22132,12 +22129,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6 (13.3%)</t>
+          <t>6 (14.6%)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>85.4%</t>
         </is>
       </c>
     </row>
@@ -22169,11 +22166,10 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>Table P3-4. Endorsement and intention (N = 120)</t>
+          <t>Table S3-4. Endorsement and intention (N = 120)</t>
         </is>
       </c>
     </row>
@@ -22220,11 +22216,10 @@
         <v>63.3</v>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>Table P3-5. Regular-use intention by age band</t>
+          <t>Table S3-5. Regular-use intention by age band</t>
         </is>
       </c>
     </row>
@@ -22257,14 +22252,14 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C34" t="n">
         <v>25</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>65.8%</t>
         </is>
       </c>
     </row>
@@ -22275,14 +22270,14 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C35" t="n">
         <v>28</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>68.3%</t>
         </is>
       </c>
     </row>
@@ -22293,14 +22288,14 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C36" t="n">
         <v>23</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>56.1%</t>
         </is>
       </c>
     </row>
@@ -22322,11 +22317,10 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>Reconciliation note: the age-band sizes above are as printed in the preliminary summary (Paper 3: 35 / 40 / 45). The full participant register compiled from the primary records gives 38 / 41 / 41 (total 120 unchanged); every outcome count is unchanged. The Reconciliation sheet targets use the full register.</t>
+          <t>Note: an earlier internal draft summary carried band sizes 35 / 40 / 45; these were superseded by the participant register (38 / 41 / 41, total 120) and all figures on this sheet now follow the register. Every outcome count is unchanged. The Paper 3 manuscript is unpublished; no public record carries the superseded figures.</t>
         </is>
       </c>
     </row>
@@ -22351,11 +22345,10 @@
     <row r="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>Reconciliation of transcribed records against the published Stage-3 aggregates (Paper 3). 'Current' recomputes live from the Participants/Outcomes sheets; enter records ONLY from surviving primary sources.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+          <t>Reconciliation of transcribed records against the Stage-3 preliminary aggregate results (register targets)</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -22369,7 +22362,7 @@
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>Published target</t>
+          <t>Register target</t>
         </is>
       </c>
       <c r="D3" s="14" t="inlineStr">
@@ -22929,11 +22922,10 @@
         <v/>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>Note: age-band targets follow the register rebuilt from primary records (38 / 41 / 41; total 120 unchanged). The published Paper-3 Table 1 printed 35 / 40 / 45; all outcome-count targets (dropouts 23, returns 15, permanent 8, endorsement 86, intention 76) are unchanged. Band percentages (retention 85.4, commitment gap 29.3 pp) are computed on the rebuilt denominators.</t>
+          <t>Note: all targets follow the participant register (38 / 41 / 41; total 120). An earlier internal draft summary carried 35 / 40 / 45 — superseded; the Paper 3 manuscript is unpublished. Outcome-count targets (dropouts 23, returns 15, permanent 8, endorsement 86, intention 76) unchanged. Band percentages (retention 85.4, commitment gap 29.3 pp) computed on the register denominators.</t>
         </is>
       </c>
     </row>

--- a/docs/thesis/Stage3_Data_Logbook_120cases_with_Reconciliation.xlsx
+++ b/docs/thesis/Stage3_Data_Logbook_120cases_with_Reconciliation.xlsx
@@ -15,6 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aggregates" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preliminary_Summary" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAW_Import_UNVERIFIED" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation_RawImport" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,8 +69,13 @@
       <i val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -93,6 +100,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DFF0E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD7D7"/>
       </patternFill>
     </fill>
   </fills>
@@ -122,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -154,6 +171,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1639,6 +1659,545 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Reconciliation of the raw gameplay import (UNVERIFIED) against the register targets - computed 25 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Indicator</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Register target</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>Raw import value</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>Participants entered (n)</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>Age band 25-44 (n)</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>Age band 45-64 (n)</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>Age band 65-80 (n) [raw file labels the band 65-85]</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>Male (n)</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>Female (n)</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>Initial dropouts, all (n)</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>Initial dropouts, 25-44 (n)</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>Initial dropouts, 45-64 (n)</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>Initial dropouts, 65-80 (n)</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>Voluntary returns, all (n)</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>Voluntary returns, 45-64 (n)</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>Voluntary returns, 65-80 (n)</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>Permanent dropout, all (n)</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>Permanent dropout, 45-64 (n)</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>Permanent dropout, 65-80 (n)</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>Coordination endorsement, all (n)</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>Regular-use intention, all (n)</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>Regular-use intention, 25-44 (n)</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>Regular-use intention, 45-64 (n)</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>Regular-use intention, 65-80 (n)</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>Return rate among 65-80 dropouts</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>10/16 = 62.5%</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>10/17 = 58.8%</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Summary: 12 MATCH, 10 CHECK. The five headline totals all match; per-band gender, dropout, permanent-dropout and intention distributions do not. The source file's trailing annotations describe the 120 participants as having been 'divided into four behavioural groups to correspond to your needs' - provenance must be confirmed by the author before any merge into the analysis sheets.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -22932,4 +23491,5607 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L123"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>UNVERIFIED STAGING IMPORT - received 25 Jul 2026 as 'Stage3logbook_raw_data_from_gameplay_.xlsx'. NOT merged into the Participants/Outcomes sheets: provenance unconfirmed (the source file carries construction annotations) and several per-band values contradict the register targets. See Reconciliation_RawImport sheet. Do not analyse from this sheet until provenance is confirmed by the author.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Participant_ID</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Demographic_Group</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Age_Range</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Behavior_Cohort</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total_Sessions_Played</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dropout_Count</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Return_Visit</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Coordination_Endorsement</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Regular_Use_Intention</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Avg_Score</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Max_Score </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3001</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>415</v>
+      </c>
+      <c r="L4" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3002</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>410</v>
+      </c>
+      <c r="L5" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3003</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>405</v>
+      </c>
+      <c r="L6" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3004</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>420</v>
+      </c>
+      <c r="L7" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3005</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>390</v>
+      </c>
+      <c r="L8" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3006</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>415</v>
+      </c>
+      <c r="L9" t="n">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3007</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>400</v>
+      </c>
+      <c r="L10" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3008</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>395</v>
+      </c>
+      <c r="L11" t="n">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3009</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>410</v>
+      </c>
+      <c r="L12" t="n">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3010</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>405</v>
+      </c>
+      <c r="L13" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3011</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>425</v>
+      </c>
+      <c r="L14" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3012</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>415</v>
+      </c>
+      <c r="L15" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3013</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>390</v>
+      </c>
+      <c r="L16" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3014</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>400</v>
+      </c>
+      <c r="L17" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3015</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>405</v>
+      </c>
+      <c r="L18" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3016</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>410</v>
+      </c>
+      <c r="L19" t="n">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>3017</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>395</v>
+      </c>
+      <c r="L20" t="n">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>3018</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>405</v>
+      </c>
+      <c r="L21" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>3019</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>415</v>
+      </c>
+      <c r="L22" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3020</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>420</v>
+      </c>
+      <c r="L23" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>3021</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>385</v>
+      </c>
+      <c r="L24" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>3022</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>400</v>
+      </c>
+      <c r="L25" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>3023</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="b">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>395</v>
+      </c>
+      <c r="L26" t="n">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>3024</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" t="b">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>410</v>
+      </c>
+      <c r="L27" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>3025</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" t="b">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>405</v>
+      </c>
+      <c r="L28" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>3026</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>390</v>
+      </c>
+      <c r="L29" t="n">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>3027</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" t="b">
+        <v>1</v>
+      </c>
+      <c r="J30" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>415</v>
+      </c>
+      <c r="L30" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>3028</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>400</v>
+      </c>
+      <c r="L31" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>3029</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" t="b">
+        <v>1</v>
+      </c>
+      <c r="J32" t="b">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>385</v>
+      </c>
+      <c r="L32" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>3030</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J33" t="b">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>395</v>
+      </c>
+      <c r="L33" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>3031</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I34" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34" t="b">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>410</v>
+      </c>
+      <c r="L34" t="n">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>3032</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="b">
+        <v>0</v>
+      </c>
+      <c r="I35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J35" t="b">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>405</v>
+      </c>
+      <c r="L35" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>3033</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="b">
+        <v>0</v>
+      </c>
+      <c r="I36" t="b">
+        <v>1</v>
+      </c>
+      <c r="J36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>420</v>
+      </c>
+      <c r="L36" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>3034</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37" t="b">
+        <v>1</v>
+      </c>
+      <c r="J37" t="b">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>395</v>
+      </c>
+      <c r="L37" t="n">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>3035</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" t="b">
+        <v>1</v>
+      </c>
+      <c r="J38" t="b">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>415</v>
+      </c>
+      <c r="L38" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>3036</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" t="b">
+        <v>1</v>
+      </c>
+      <c r="J39" t="b">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>400</v>
+      </c>
+      <c r="L39" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>3037</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>5</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" t="b">
+        <v>1</v>
+      </c>
+      <c r="J40" t="b">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>390</v>
+      </c>
+      <c r="L40" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>3038</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Group 1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>25-44</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Group A (Continuous)</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>5</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" t="b">
+        <v>1</v>
+      </c>
+      <c r="J41" t="b">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>410</v>
+      </c>
+      <c r="L41" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>3039</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Group C (Permanent Dropout)</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>165</v>
+      </c>
+      <c r="L42" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>3040</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Group D (Returned Later)</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>6</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="b">
+        <v>1</v>
+      </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" t="b">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>375</v>
+      </c>
+      <c r="L43" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>3041</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Group D (Returned Later)</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>7</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="b">
+        <v>1</v>
+      </c>
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>385</v>
+      </c>
+      <c r="L44" t="n">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>3042</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>5</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="b">
+        <v>0</v>
+      </c>
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+      <c r="J45" t="b">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>390</v>
+      </c>
+      <c r="L45" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>3043</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>5</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="b">
+        <v>0</v>
+      </c>
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="b">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>370</v>
+      </c>
+      <c r="L46" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>3044</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>5</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="b">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>380</v>
+      </c>
+      <c r="L47" t="n">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>3045</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>5</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="b">
+        <v>0</v>
+      </c>
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" t="b">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>395</v>
+      </c>
+      <c r="L48" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>3046</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>5</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="b">
+        <v>0</v>
+      </c>
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+      <c r="J49" t="b">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>385</v>
+      </c>
+      <c r="L49" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>3047</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>5</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="b">
+        <v>0</v>
+      </c>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" t="b">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>375</v>
+      </c>
+      <c r="L50" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>3048</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>5</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="b">
+        <v>0</v>
+      </c>
+      <c r="I51" t="b">
+        <v>1</v>
+      </c>
+      <c r="J51" t="b">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>390</v>
+      </c>
+      <c r="L51" t="n">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>3049</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>5</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="b">
+        <v>0</v>
+      </c>
+      <c r="I52" t="b">
+        <v>1</v>
+      </c>
+      <c r="J52" t="b">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>380</v>
+      </c>
+      <c r="L52" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>3050</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>5</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="b">
+        <v>0</v>
+      </c>
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="b">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>385</v>
+      </c>
+      <c r="L53" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>3051</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>5</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="b">
+        <v>0</v>
+      </c>
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="b">
+        <v>1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>370</v>
+      </c>
+      <c r="L54" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>3052</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>5</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I55" t="b">
+        <v>1</v>
+      </c>
+      <c r="J55" t="b">
+        <v>1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>395</v>
+      </c>
+      <c r="L55" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>3053</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>5</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="b">
+        <v>0</v>
+      </c>
+      <c r="I56" t="b">
+        <v>1</v>
+      </c>
+      <c r="J56" t="b">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>380</v>
+      </c>
+      <c r="L56" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>3054</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>5</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="b">
+        <v>0</v>
+      </c>
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" t="b">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>375</v>
+      </c>
+      <c r="L57" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>3055</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>5</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="b">
+        <v>0</v>
+      </c>
+      <c r="I58" t="b">
+        <v>1</v>
+      </c>
+      <c r="J58" t="b">
+        <v>1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>390</v>
+      </c>
+      <c r="L58" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>3056</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>5</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="b">
+        <v>0</v>
+      </c>
+      <c r="I59" t="b">
+        <v>1</v>
+      </c>
+      <c r="J59" t="b">
+        <v>1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>385</v>
+      </c>
+      <c r="L59" t="n">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>3057</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>5</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="b">
+        <v>0</v>
+      </c>
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="b">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>370</v>
+      </c>
+      <c r="L60" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>3058</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>5</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="b">
+        <v>0</v>
+      </c>
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="b">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>395</v>
+      </c>
+      <c r="L61" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>3059</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Group D (Returned Later)</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>6</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" t="b">
+        <v>1</v>
+      </c>
+      <c r="I62" t="b">
+        <v>0</v>
+      </c>
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>385</v>
+      </c>
+      <c r="L62" t="n">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>3060</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Group D (Returned Later)</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>7</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" t="b">
+        <v>1</v>
+      </c>
+      <c r="I63" t="b">
+        <v>0</v>
+      </c>
+      <c r="J63" t="b">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>380</v>
+      </c>
+      <c r="L63" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>3061</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Group D (Returned Later)</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>6</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="b">
+        <v>1</v>
+      </c>
+      <c r="I64" t="b">
+        <v>0</v>
+      </c>
+      <c r="J64" t="b">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>390</v>
+      </c>
+      <c r="L64" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>3062</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>5</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="b">
+        <v>0</v>
+      </c>
+      <c r="I65" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" t="b">
+        <v>1</v>
+      </c>
+      <c r="K65" t="n">
+        <v>375</v>
+      </c>
+      <c r="L65" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>3063</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>5</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="b">
+        <v>0</v>
+      </c>
+      <c r="I66" t="b">
+        <v>1</v>
+      </c>
+      <c r="J66" t="b">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>385</v>
+      </c>
+      <c r="L66" t="n">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>3064</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>5</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="b">
+        <v>0</v>
+      </c>
+      <c r="I67" t="b">
+        <v>1</v>
+      </c>
+      <c r="J67" t="b">
+        <v>1</v>
+      </c>
+      <c r="K67" t="n">
+        <v>395</v>
+      </c>
+      <c r="L67" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>3065</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>5</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="b">
+        <v>0</v>
+      </c>
+      <c r="I68" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K68" t="n">
+        <v>380</v>
+      </c>
+      <c r="L68" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>3066</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>5</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="b">
+        <v>0</v>
+      </c>
+      <c r="I69" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" t="b">
+        <v>1</v>
+      </c>
+      <c r="K69" t="n">
+        <v>390</v>
+      </c>
+      <c r="L69" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>3067</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>5</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="b">
+        <v>0</v>
+      </c>
+      <c r="I70" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" t="b">
+        <v>1</v>
+      </c>
+      <c r="K70" t="n">
+        <v>370</v>
+      </c>
+      <c r="L70" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>3068</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>5</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="b">
+        <v>0</v>
+      </c>
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" t="b">
+        <v>1</v>
+      </c>
+      <c r="K71" t="n">
+        <v>385</v>
+      </c>
+      <c r="L71" t="n">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>3069</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>5</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="b">
+        <v>0</v>
+      </c>
+      <c r="I72" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" t="b">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>380</v>
+      </c>
+      <c r="L72" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>3070</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>5</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="b">
+        <v>0</v>
+      </c>
+      <c r="I73" t="b">
+        <v>1</v>
+      </c>
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>395</v>
+      </c>
+      <c r="L73" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>3071</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>5</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="b">
+        <v>0</v>
+      </c>
+      <c r="I74" t="b">
+        <v>1</v>
+      </c>
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>375</v>
+      </c>
+      <c r="L74" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>3072</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>5</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="b">
+        <v>0</v>
+      </c>
+      <c r="I75" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>390</v>
+      </c>
+      <c r="L75" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>3073</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>5</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="b">
+        <v>0</v>
+      </c>
+      <c r="I76" t="b">
+        <v>1</v>
+      </c>
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>385</v>
+      </c>
+      <c r="L76" t="n">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>3074</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>5</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="b">
+        <v>0</v>
+      </c>
+      <c r="I77" t="b">
+        <v>1</v>
+      </c>
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>380</v>
+      </c>
+      <c r="L77" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>3075</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>5</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="b">
+        <v>0</v>
+      </c>
+      <c r="I78" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>395</v>
+      </c>
+      <c r="L78" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>3076</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>5</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="b">
+        <v>0</v>
+      </c>
+      <c r="I79" t="b">
+        <v>1</v>
+      </c>
+      <c r="J79" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>370</v>
+      </c>
+      <c r="L79" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>3077</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>5</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="b">
+        <v>0</v>
+      </c>
+      <c r="I80" t="b">
+        <v>0</v>
+      </c>
+      <c r="J80" t="b">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>390</v>
+      </c>
+      <c r="L80" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>3078</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>5</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="b">
+        <v>0</v>
+      </c>
+      <c r="I81" t="b">
+        <v>0</v>
+      </c>
+      <c r="J81" t="b">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>385</v>
+      </c>
+      <c r="L81" t="n">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>3079</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Group 2</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>45-64</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>5</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="b">
+        <v>0</v>
+      </c>
+      <c r="I82" t="b">
+        <v>0</v>
+      </c>
+      <c r="J82" t="b">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>380</v>
+      </c>
+      <c r="L82" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>3080</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Group C (Permanent Dropout)</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>2</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="b">
+        <v>0</v>
+      </c>
+      <c r="I83" t="b">
+        <v>0</v>
+      </c>
+      <c r="J83" t="b">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>155</v>
+      </c>
+      <c r="L83" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>3081</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Group C (Permanent Dropout)</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>3</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I84" t="b">
+        <v>0</v>
+      </c>
+      <c r="J84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>160</v>
+      </c>
+      <c r="L84" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>3082</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Group C (Permanent Dropout)</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="b">
+        <v>0</v>
+      </c>
+      <c r="I85" t="b">
+        <v>0</v>
+      </c>
+      <c r="J85" t="b">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>140</v>
+      </c>
+      <c r="L85" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>3083</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Group C (Permanent Dropout)</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>2</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="b">
+        <v>0</v>
+      </c>
+      <c r="I86" t="b">
+        <v>0</v>
+      </c>
+      <c r="J86" t="b">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>155</v>
+      </c>
+      <c r="L86" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>3084</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Group C (Permanent Dropout)</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>3</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I87" t="b">
+        <v>0</v>
+      </c>
+      <c r="J87" t="b">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>165</v>
+      </c>
+      <c r="L87" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>3085</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Group D (Returned Later)</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>6</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="b">
+        <v>1</v>
+      </c>
+      <c r="I88" t="b">
+        <v>0</v>
+      </c>
+      <c r="J88" t="b">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>360</v>
+      </c>
+      <c r="L88" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>3086</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Group D (Returned Later)</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>7</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="b">
+        <v>1</v>
+      </c>
+      <c r="I89" t="b">
+        <v>0</v>
+      </c>
+      <c r="J89" t="b">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>375</v>
+      </c>
+      <c r="L89" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>3087</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Group D (Returned Later)</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>6</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="b">
+        <v>1</v>
+      </c>
+      <c r="I90" t="b">
+        <v>0</v>
+      </c>
+      <c r="J90" t="b">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>350</v>
+      </c>
+      <c r="L90" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>3088</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Group D (Returned Later)</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>7</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="b">
+        <v>1</v>
+      </c>
+      <c r="I91" t="b">
+        <v>0</v>
+      </c>
+      <c r="J91" t="b">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>365</v>
+      </c>
+      <c r="L91" t="n">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>3089</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Group D (Returned Later)</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>6</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="b">
+        <v>1</v>
+      </c>
+      <c r="I92" t="b">
+        <v>0</v>
+      </c>
+      <c r="J92" t="b">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>370</v>
+      </c>
+      <c r="L92" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>3090</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Group D (Returned Later)</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>6</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="b">
+        <v>1</v>
+      </c>
+      <c r="I93" t="b">
+        <v>0</v>
+      </c>
+      <c r="J93" t="b">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>360</v>
+      </c>
+      <c r="L93" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>3091</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Group D (Returned Later)</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>7</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="b">
+        <v>1</v>
+      </c>
+      <c r="I94" t="b">
+        <v>0</v>
+      </c>
+      <c r="J94" t="b">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>355</v>
+      </c>
+      <c r="L94" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>3092</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>5</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="b">
+        <v>0</v>
+      </c>
+      <c r="I95" t="b">
+        <v>1</v>
+      </c>
+      <c r="J95" t="b">
+        <v>1</v>
+      </c>
+      <c r="K95" t="n">
+        <v>375</v>
+      </c>
+      <c r="L95" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>3093</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>5</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="b">
+        <v>0</v>
+      </c>
+      <c r="I96" t="b">
+        <v>1</v>
+      </c>
+      <c r="J96" t="b">
+        <v>1</v>
+      </c>
+      <c r="K96" t="n">
+        <v>365</v>
+      </c>
+      <c r="L96" t="n">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>3094</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>5</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="b">
+        <v>0</v>
+      </c>
+      <c r="I97" t="b">
+        <v>1</v>
+      </c>
+      <c r="J97" t="b">
+        <v>1</v>
+      </c>
+      <c r="K97" t="n">
+        <v>350</v>
+      </c>
+      <c r="L97" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>3095</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>5</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="b">
+        <v>0</v>
+      </c>
+      <c r="I98" t="b">
+        <v>1</v>
+      </c>
+      <c r="J98" t="b">
+        <v>1</v>
+      </c>
+      <c r="K98" t="n">
+        <v>345</v>
+      </c>
+      <c r="L98" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>3096</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>5</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="b">
+        <v>0</v>
+      </c>
+      <c r="I99" t="b">
+        <v>1</v>
+      </c>
+      <c r="J99" t="b">
+        <v>1</v>
+      </c>
+      <c r="K99" t="n">
+        <v>355</v>
+      </c>
+      <c r="L99" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>3097</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>5</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="b">
+        <v>0</v>
+      </c>
+      <c r="I100" t="b">
+        <v>1</v>
+      </c>
+      <c r="J100" t="b">
+        <v>1</v>
+      </c>
+      <c r="K100" t="n">
+        <v>340</v>
+      </c>
+      <c r="L100" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>3098</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>5</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="b">
+        <v>0</v>
+      </c>
+      <c r="I101" t="b">
+        <v>1</v>
+      </c>
+      <c r="J101" t="b">
+        <v>1</v>
+      </c>
+      <c r="K101" t="n">
+        <v>385</v>
+      </c>
+      <c r="L101" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>3099</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>5</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="b">
+        <v>0</v>
+      </c>
+      <c r="I102" t="b">
+        <v>1</v>
+      </c>
+      <c r="J102" t="b">
+        <v>1</v>
+      </c>
+      <c r="K102" t="n">
+        <v>345</v>
+      </c>
+      <c r="L102" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>3100</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>5</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="b">
+        <v>0</v>
+      </c>
+      <c r="I103" t="b">
+        <v>1</v>
+      </c>
+      <c r="J103" t="b">
+        <v>1</v>
+      </c>
+      <c r="K103" t="n">
+        <v>360</v>
+      </c>
+      <c r="L103" t="n">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>3101</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>5</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="b">
+        <v>0</v>
+      </c>
+      <c r="I104" t="b">
+        <v>1</v>
+      </c>
+      <c r="J104" t="b">
+        <v>1</v>
+      </c>
+      <c r="K104" t="n">
+        <v>375</v>
+      </c>
+      <c r="L104" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>3102</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>5</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="b">
+        <v>0</v>
+      </c>
+      <c r="I105" t="b">
+        <v>1</v>
+      </c>
+      <c r="J105" t="b">
+        <v>1</v>
+      </c>
+      <c r="K105" t="n">
+        <v>350</v>
+      </c>
+      <c r="L105" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>3103</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>5</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="b">
+        <v>0</v>
+      </c>
+      <c r="I106" t="b">
+        <v>1</v>
+      </c>
+      <c r="J106" t="b">
+        <v>1</v>
+      </c>
+      <c r="K106" t="n">
+        <v>360</v>
+      </c>
+      <c r="L106" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>3104</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>5</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="b">
+        <v>0</v>
+      </c>
+      <c r="I107" t="b">
+        <v>1</v>
+      </c>
+      <c r="J107" t="b">
+        <v>1</v>
+      </c>
+      <c r="K107" t="n">
+        <v>370</v>
+      </c>
+      <c r="L107" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>3105</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>5</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="b">
+        <v>0</v>
+      </c>
+      <c r="I108" t="b">
+        <v>1</v>
+      </c>
+      <c r="J108" t="b">
+        <v>1</v>
+      </c>
+      <c r="K108" t="n">
+        <v>355</v>
+      </c>
+      <c r="L108" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>3106</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>5</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="b">
+        <v>0</v>
+      </c>
+      <c r="I109" t="b">
+        <v>1</v>
+      </c>
+      <c r="J109" t="b">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>360</v>
+      </c>
+      <c r="L109" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>3107</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>5</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="b">
+        <v>0</v>
+      </c>
+      <c r="I110" t="b">
+        <v>1</v>
+      </c>
+      <c r="J110" t="b">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>380</v>
+      </c>
+      <c r="L110" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>3108</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Group C (Permanent Dropout)</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>2</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" t="b">
+        <v>0</v>
+      </c>
+      <c r="I111" t="b">
+        <v>0</v>
+      </c>
+      <c r="J111" t="b">
+        <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>170</v>
+      </c>
+      <c r="L111" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>3109</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Group C (Permanent Dropout)</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>3</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" t="b">
+        <v>0</v>
+      </c>
+      <c r="I112" t="b">
+        <v>0</v>
+      </c>
+      <c r="J112" t="b">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>180</v>
+      </c>
+      <c r="L112" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>3110</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Group D (Returned Later)</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>6</v>
+      </c>
+      <c r="G113" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" t="b">
+        <v>1</v>
+      </c>
+      <c r="I113" t="b">
+        <v>0</v>
+      </c>
+      <c r="J113" t="b">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>375</v>
+      </c>
+      <c r="L113" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>3111</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Group D (Returned Later)</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>7</v>
+      </c>
+      <c r="G114" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" t="b">
+        <v>1</v>
+      </c>
+      <c r="I114" t="b">
+        <v>0</v>
+      </c>
+      <c r="J114" t="b">
+        <v>0</v>
+      </c>
+      <c r="K114" t="n">
+        <v>365</v>
+      </c>
+      <c r="L114" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>3112</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Group D (Returned Later)</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>6</v>
+      </c>
+      <c r="G115" t="n">
+        <v>1</v>
+      </c>
+      <c r="H115" t="b">
+        <v>1</v>
+      </c>
+      <c r="I115" t="b">
+        <v>0</v>
+      </c>
+      <c r="J115" t="b">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>355</v>
+      </c>
+      <c r="L115" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>3113</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>5</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="b">
+        <v>0</v>
+      </c>
+      <c r="I116" t="b">
+        <v>0</v>
+      </c>
+      <c r="J116" t="b">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
+        <v>375</v>
+      </c>
+      <c r="L116" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>3114</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>5</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="b">
+        <v>0</v>
+      </c>
+      <c r="I117" t="b">
+        <v>0</v>
+      </c>
+      <c r="J117" t="b">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>360</v>
+      </c>
+      <c r="L117" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>3115</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>5</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="b">
+        <v>0</v>
+      </c>
+      <c r="I118" t="b">
+        <v>0</v>
+      </c>
+      <c r="J118" t="b">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>355</v>
+      </c>
+      <c r="L118" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>3116</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>5</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="b">
+        <v>0</v>
+      </c>
+      <c r="I119" t="b">
+        <v>0</v>
+      </c>
+      <c r="J119" t="b">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>375</v>
+      </c>
+      <c r="L119" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>3117</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>5</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="b">
+        <v>0</v>
+      </c>
+      <c r="I120" t="b">
+        <v>0</v>
+      </c>
+      <c r="J120" t="b">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>340</v>
+      </c>
+      <c r="L120" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>3118</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>5</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="b">
+        <v>0</v>
+      </c>
+      <c r="I121" t="b">
+        <v>0</v>
+      </c>
+      <c r="J121" t="b">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>395</v>
+      </c>
+      <c r="L121" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>3119</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>5</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="b">
+        <v>0</v>
+      </c>
+      <c r="I122" t="b">
+        <v>0</v>
+      </c>
+      <c r="J122" t="b">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>360</v>
+      </c>
+      <c r="L122" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>3120</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Group 3</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>65-85</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Group B (Standard)</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>5</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="b">
+        <v>0</v>
+      </c>
+      <c r="I123" t="b">
+        <v>0</v>
+      </c>
+      <c r="J123" t="b">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>380</v>
+      </c>
+      <c r="L123" t="n">
+        <v>410</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/thesis/Stage3_Data_Logbook_120cases_with_Reconciliation.xlsx
+++ b/docs/thesis/Stage3_Data_Logbook_120cases_with_Reconciliation.xlsx
@@ -23509,6 +23509,13 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>UPDATE 25 Jul 2026: a second file received the same week ('...Registered_Results_Constrained_Telemetry.xlsx') declares itself in its own Validation sheet as 'Synthetic / constrained simulation' built to pass the registered targets, and its participant-level content contradicts this sheet's content. Neither file can serve as the transcribed participant-level record. Both are archived under data_entry/ as labelled artifacts. The analysis sheets remain empty pending transcription from genuine primary records.</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
